--- a/physique/2/dev_A1/ressources/Labo 3.1 - Interférence d'ondes.xlsx
+++ b/physique/2/dev_A1/ressources/Labo 3.1 - Interférence d'ondes.xlsx
@@ -21,9 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
-  <si>
-    <t xml:space="preserve">Fréquence / Hz ±</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">Fréquence / Hz ±1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position minima ±1 \ mm </t>
   </si>
   <si>
     <t xml:space="preserve">Position minima / mm ±1</t>
@@ -72,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gamma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sous</t>
   </si>
   <si>
     <t xml:space="preserve">Rapport de grossissement</t>
@@ -146,17 +152,16 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -172,6 +177,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -228,20 +239,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -396,7 +411,7 @@
             <c:numRef>
               <c:f>'Manip. 1 '!$F$2:$F$11</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.00111111111111111</c:v>
@@ -472,11 +487,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="83549175"/>
-        <c:axId val="26405342"/>
+        <c:axId val="11681137"/>
+        <c:axId val="51472009"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="83549175"/>
+        <c:axId val="11681137"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -552,12 +567,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26405342"/>
+        <c:crossAx val="51472009"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="26405342"/>
+        <c:axId val="51472009"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -633,7 +648,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83549175"/>
+        <c:crossAx val="11681137"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -794,11 +809,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="32398518"/>
-        <c:axId val="4131108"/>
+        <c:axId val="61051566"/>
+        <c:axId val="61777587"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32398518"/>
+        <c:axId val="61051566"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.003"/>
@@ -875,12 +890,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4131108"/>
+        <c:crossAx val="61777587"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="4131108"/>
+        <c:axId val="61777587"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.51"/>
@@ -958,7 +973,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32398518"/>
+        <c:crossAx val="61051566"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -996,10 +1011,10 @@
       <xdr:rowOff>122400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>545400</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1626480</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>147960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1007,8 +1022,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2260800" y="2321280"/>
-        <a:ext cx="6161760" cy="2694960"/>
+        <a:off x="2561760" y="2225520"/>
+        <a:ext cx="6161400" cy="2694600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1032,9 +1047,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>158400</xdr:colOff>
+      <xdr:colOff>158040</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1042,8 +1057,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="12870360" y="1351080"/>
-        <a:ext cx="5085720" cy="2736000"/>
+        <a:off x="12870360" y="1256400"/>
+        <a:ext cx="5085360" cy="2735640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1099,14 +1114,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1114,67 +1129,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1193,35 +1166,11 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -1233,476 +1182,491 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="21.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>291</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">C2-B2</f>
         <v>192</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <f aca="false">2*D2*10^-3</f>
         <v>0.384</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="2" t="n">
         <f aca="false">1/A2</f>
         <v>0.00111111111111111</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="3" t="n">
         <f aca="false">J2+273.15</f>
         <v>296.55</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">2*L2*10^-3</f>
         <v>0.384</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">C3-B3</f>
         <v>135</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <f aca="false">2*D3*10^-3</f>
         <v>0.27</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="2" t="n">
         <f aca="false">1/A3</f>
         <v>0.000769230769230769</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">2*L3*10^-3</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>1700</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">C4-B4</f>
         <v>103</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">2*D4*10^-3</f>
         <v>0.206</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="2" t="n">
         <f aca="false">1/A4</f>
         <v>0.000588235294117647</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">2*L4*10^-3</f>
         <v>0.206</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>2150</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">C5-B5</f>
         <v>81</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">2*D5*10^-3</f>
         <v>0.162</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="2" t="n">
         <f aca="false">1/A5</f>
         <v>0.000465116279069767</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <f aca="false">2*L5*10^-3</f>
         <v>0.162</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>2550</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">C6-B6</f>
         <v>68</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">2*D6*10^-3</f>
         <v>0.136</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <f aca="false">1/A6</f>
         <v>0.000392156862745098</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <f aca="false">2*L6*10^-3</f>
         <v>0.136</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">C7-B7</f>
         <v>57</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="false">2*D7*10^-3</f>
         <v>0.114</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <f aca="false">1/A7</f>
         <v>0.000333333333333333</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>206</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>262</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <f aca="false">(I7-B7)/4</f>
         <v>57</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <f aca="false">2*L7*10^-3</f>
         <v>0.114</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">C8-B8</f>
         <v>49</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">2*D8*10^-3</f>
         <v>0.098</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <f aca="false">1/A8</f>
         <v>0.000285714285714286</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <f aca="false">(J8-B8)/5</f>
         <v>49.6</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <f aca="false">2*L8*10^-3</f>
         <v>0.0992</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">C9-B9</f>
         <v>43</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">2*D9*10^-3</f>
         <v>0.086</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <f aca="false">1/A9</f>
         <v>0.00025</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>244</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <f aca="false">(J9-B9)/5</f>
         <v>43.2</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <f aca="false">2*L9*10^-3</f>
         <v>0.0864</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">C10-B10</f>
         <v>38</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">2*D10*10^-3</f>
         <v>0.076</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <f aca="false">1/A10</f>
         <v>0.000222222222222222</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>183</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>222</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <f aca="false">(J10-B10)/5</f>
         <v>38.4</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <f aca="false">2*L10*10^-3</f>
         <v>0.0768</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <f aca="false">C11-B11</f>
         <v>34</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <f aca="false">2*D11*10^-3</f>
         <v>0.068</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <f aca="false">1/A11</f>
         <v>0.0002</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <f aca="false">(J11-B11)/5</f>
         <v>35</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <f aca="false">2*L11*10^-3</f>
         <v>0.07</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="0" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I16" s="0" t="n">
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="1" t="n">
         <f aca="false" t="array" ref="I16:J17">LINEST(M2:M11,F2:F11,1,1)</f>
         <v>347.499420102444</v>
       </c>
-      <c r="J16" s="0" t="n">
-        <v>-4.65772899255201E-006</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H17" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="0" t="n">
-        <v>1.74808729514849</v>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>0.000939269813671122</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I18" s="0" t="s">
+      <c r="J16" s="1" t="n">
+        <v>-4.65772899260752E-006</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="0" t="s">
+      <c r="I17" s="1" t="n">
+        <v>1.74808729514842</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>0.000939269813671084</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="J18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N18" s="0" t="s">
+      <c r="M18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O18" s="0" t="s">
+      <c r="N18" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L19" s="0" t="n">
+      <c r="O18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L19" s="1" t="n">
         <f aca="false">SQRT((M19*O19*K2)/N19)</f>
         <v>345.211276852164</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <v>8.314</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <v>0.0289645</v>
       </c>
-      <c r="O19" s="0" t="n">
+      <c r="O19" s="1" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1725,480 +1689,486 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <f aca="false">E2/D2</f>
         <v>1.6697247706422</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>54.5</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>21.5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <f aca="false">E4/D4</f>
         <v>1.6734693877551</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <f aca="false">AVERAGE(A4,A2,A2)</f>
         <v>1.6709729763465</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>11.5</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <f aca="false">A8*10^-3</f>
         <v>0.0115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H10" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="0" t="s">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="0" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="I11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>14.8</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <f aca="false">40/2</f>
         <v>20</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="3" t="n">
         <f aca="false">B12</f>
         <v>20</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <f aca="false">1/A12</f>
         <v>0.0675675675675676</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">F12*10^-3*A12</f>
         <v>0.296</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="1" t="n">
         <f aca="false">F12*10^-3</f>
         <v>0.02</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">I12/$A$5</f>
         <v>0.0119690744752372</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <f aca="false">53/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="3" t="n">
         <f aca="false">B13</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <f aca="false">1/A13</f>
         <v>0.0555555555555556</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">F13*10^-3*A13</f>
         <v>0.318</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="1" t="n">
         <f aca="false">F13*10^-3</f>
         <v>0.0176666666666667</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <f aca="false">I13/$A$5</f>
         <v>0.0105726824531262</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>20.9</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <f aca="false">48/3</f>
         <v>16</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="3" t="n">
         <f aca="false">B14</f>
         <v>16</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <f aca="false">1/A14</f>
         <v>0.0478468899521531</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <f aca="false">F14*10^-3*A14</f>
         <v>0.3344</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="1" t="n">
         <f aca="false">F14*10^-3</f>
         <v>0.016</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <f aca="false">I14/$A$5</f>
         <v>0.00957525958018974</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <f aca="false">47/4</f>
         <v>11.75</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="3" t="n">
         <f aca="false">B15</f>
         <v>11.75</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <f aca="false">1/A15</f>
         <v>0.032258064516129</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <f aca="false">F15*10^-3*A15</f>
         <v>0.36425</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="1" t="n">
         <f aca="false">F15*10^-3</f>
         <v>0.01175</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <f aca="false">I15/$A$5</f>
         <v>0.00703183125420184</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
         <v>40.6</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <f aca="false">60/6</f>
         <v>10</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="3" t="n">
         <f aca="false">B16</f>
         <v>10</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <f aca="false">1/A16</f>
         <v>0.0246305418719212</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">F16*10^-3*A16</f>
         <v>0.406</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="1" t="n">
         <f aca="false">F16*10^-3</f>
         <v>0.01</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="1" t="n">
         <f aca="false">I16/$A$5</f>
         <v>0.00598453723761859</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
         <v>49.6</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <f aca="false">60 /7</f>
         <v>8.57142857142857</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="3" t="n">
         <f aca="false">B17</f>
         <v>8.57142857142857</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <f aca="false">1/A17</f>
         <v>0.0201612903225806</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="1" t="n">
         <f aca="false">F17*10^-3*A17</f>
         <v>0.425142857142857</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="1" t="n">
         <f aca="false">F17*10^-3</f>
         <v>0.00857142857142857</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="1" t="n">
         <f aca="false">I17/$A$5</f>
         <v>0.00512960334653022</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
         <v>61.1</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <f aca="false">45/6</f>
         <v>7.5</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="3" t="n">
         <f aca="false">B18</f>
         <v>7.5</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <f aca="false">1/A18</f>
         <v>0.016366612111293</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="1" t="n">
         <f aca="false">F18*10^-3*A18</f>
         <v>0.45825</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="1" t="n">
         <f aca="false">F18*10^-3</f>
         <v>0.0075</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="1" t="n">
         <f aca="false">I18/$A$5</f>
         <v>0.00448840292821394</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>70.1</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <f aca="false">49/7</f>
         <v>7</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="3" t="n">
         <f aca="false">B19</f>
         <v>7</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="4" t="n">
         <f aca="false">1/A19</f>
         <v>0.014265335235378</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">F19*10^-3*A19</f>
         <v>0.4907</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="1" t="n">
         <f aca="false">F19*10^-3</f>
         <v>0.007</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="1" t="n">
         <f aca="false">I19/$A$5</f>
         <v>0.00418917606633301</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>79.2</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <f aca="false">50/8</f>
         <v>6.25</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="3" t="n">
         <f aca="false">B20</f>
         <v>6.25</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <f aca="false">1/A20</f>
         <v>0.0126262626262626</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">F20*10^-3*A20</f>
         <v>0.495</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="1" t="n">
         <f aca="false">F20*10^-3</f>
         <v>0.00625</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="1" t="n">
         <f aca="false">I20/$A$5</f>
         <v>0.00374033577351162</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="1"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="1"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="1"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="1"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="1"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="3"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
         <v>4.1</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>7.4</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <f aca="false">B30/A30</f>
         <v>1.80487804878049</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
         <v>25.2</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>113</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
         <v>19.6</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
         <v>25.2</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>41</v>
       </c>
     </row>
